--- a/business_surveys/047_research_development_evaluation_form--business_surveys.xlsx
+++ b/business_surveys/047_research_development_evaluation_form--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1245,34 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>research_methodology_choices</t>
+          <t>research_area_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>case_study</t>
+          <t>software_development</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Case Study</t>
+          <t>Software Development</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>research_methodology_choices</t>
+          <t>research_area_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>experimental_design</t>
+          <t>data_science</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Experimental Design</t>
+          <t>Data Science</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>software_development</t>
+          <t>artificial_intelligence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Software Development</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>data_science</t>
+          <t>human-computer_interaction</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Human-Computer Interaction</t>
         </is>
       </c>
     </row>
@@ -1318,46 +1318,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>artificial_intelligence</t>
+          <t>machine_learning</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Machine Learning</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>research_area_choices</t>
+          <t>next_review_status_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>human-computer_interaction</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Human-Computer Interaction</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>research_area_choices</t>
+          <t>next_review_status_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>machine_learning</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1369,46 +1369,46 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>next_review_status_choices</t>
+          <t>final_review_status_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>next_review_status_choices</t>
+          <t>final_review_status_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1420,44 +1420,10 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>final_review_status_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>final_review_status_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>rejected</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
